--- a/lca/inventories.xlsx
+++ b/lca/inventories.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lluc\Documents\VSCode_Projects\lca_methanol\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gasn2-my.sharepoint.com/personal/fgonzalez_gasn2_com/Documents/Documents/VSCode_Projects/MethanolPaper/lca/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49138196-C879-4812-B21B-7CB8123F8481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{49138196-C879-4812-B21B-7CB8123F8481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5C22335-5ACA-43B0-BC39-8DD83BA2D3EF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="methanol" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -39,9 +34,6 @@
     <t>comment</t>
   </si>
   <si>
-    <t>Simulation performed with Aspen Hysys (available in Zenodo) [potser algun comentari més com vulguis]</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
@@ -150,9 +142,6 @@
     <t>Carbon dioxide, non-fossil</t>
   </si>
   <si>
-    <t>Franc afegeix la cita aquí pls</t>
-  </si>
-  <si>
     <t>water, ultrapure</t>
   </si>
   <si>
@@ -199,17 +188,30 @@
   </si>
   <si>
     <t>market group for electricity, medium voltage</t>
+  </si>
+  <si>
+    <t>A. Franco and C. Giovannini, “Recent and future advances in water electrolysis for green hydrogen generation: Critical analysis and perspectives,” Sustainability, vol. 15, no. 24, p. 16917, Dec. 2023, doi: 10.3390/su152416917</t>
+  </si>
+  <si>
+    <t>Simulation of methanol production by CO₂ hydrogenation performed with Aspen HYSYS. Further details can be found in the associated article.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -247,7 +249,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -266,12 +268,6 @@
         <bgColor rgb="FFDEEBF6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -285,12 +281,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -298,13 +294,12 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,24 +541,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="58.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" customWidth="1"/>
-    <col min="6" max="6" width="36.28515625" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="36.33203125" customWidth="1"/>
+    <col min="7" max="7" width="26.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -572,7 +567,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -582,7 +577,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -590,80 +585,80 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
       <c r="B8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -672,197 +667,197 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="H11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="C12">
         <v>1.68</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="H12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="C13">
         <v>0.19</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
         <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
       </c>
       <c r="C14">
         <v>4.53</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="B15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15">
+        <v>0.1925</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15">
-        <v>6.39</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="B16" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
       </c>
       <c r="C16" s="6">
         <v>8.3799999999999996E-9</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="H16" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
         <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
       </c>
       <c r="C17">
         <v>8.5999999999999998E-4</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="C18">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H18" s="4" t="s">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="C19">
         <v>2.5000000000000001E-4</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -872,199 +867,199 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
         <v>5</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>7</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="H29" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C30">
         <v>8.93</v>
       </c>
       <c r="D30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="H30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C31" s="6">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="H31" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>46</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C32">
         <v>33.5</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" t="s">
         <v>27</v>
       </c>
-      <c r="G32" t="s">
-        <v>28</v>
-      </c>
       <c r="H32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C33">
         <v>7.93</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="H33" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1074,220 +1069,220 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>3</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
         <v>5</v>
       </c>
-      <c r="B37" t="s">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>7</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>10</v>
-      </c>
-      <c r="B40" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" t="s">
-        <v>16</v>
-      </c>
-      <c r="H42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>19</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>57</v>
+        <v>28</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="C44">
         <v>0.61</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C45">
         <v>24.5</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C46">
         <v>1.14E-3</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G46" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="H46" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C47" s="6">
         <v>8.4399999999999998E-10</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="H47" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="7"/>
       <c r="C51" s="5"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="C52" s="5"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>

--- a/lca/inventories.xlsx
+++ b/lca/inventories.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gasn2-my.sharepoint.com/personal/fgonzalez_gasn2_com/Documents/Documents/VSCode_Projects/MethanolPaper/lca/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{49138196-C879-4812-B21B-7CB8123F8481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5C22335-5ACA-43B0-BC39-8DD83BA2D3EF}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{49138196-C879-4812-B21B-7CB8123F8481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2512A099-913D-446F-B7B3-61DB9F62902F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="methanol" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -297,7 +310,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -315,6 +328,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1000,7 +1017,7 @@
         <v>43</v>
       </c>
       <c r="C31" s="6">
-        <v>1.5599999999999999E-2</v>
+        <v>1.6447368421052631E-4</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
